--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1420,6 +1420,276 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123321518</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Per-Larsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601084</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967962</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2024_426</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123321517</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78502</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Per-Larsmyren, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601045</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6968150</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024_427</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på stubbe</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321518</v>
+        <v>123321517</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>78505</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,47 +1437,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Larsmyran, Mpd</t>
+          <t>Per-Larsmyren, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601084</v>
+        <v>601045</v>
       </c>
       <c r="R8" t="n">
-        <v>6967962</v>
+        <v>6968150</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_426</t>
+          <t>2024_427</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321517</v>
+        <v>123321518</v>
       </c>
       <c r="B9" t="n">
-        <v>78502</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Larsmyren, Mpd</t>
+          <t>Per-Larsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601045</v>
+        <v>601084</v>
       </c>
       <c r="R9" t="n">
-        <v>6968150</v>
+        <v>6967962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_427</t>
+          <t>2024_426</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321517</v>
+        <v>123321518</v>
       </c>
       <c r="B8" t="n">
-        <v>78505</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,47 +1437,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Larsmyren, Mpd</t>
+          <t>Per-Larsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601045</v>
+        <v>601084</v>
       </c>
       <c r="R8" t="n">
-        <v>6968150</v>
+        <v>6967962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_427</t>
+          <t>2024_426</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321518</v>
+        <v>123321517</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>78507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Larsmyran, Mpd</t>
+          <t>Per-Larsmyren, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601084</v>
+        <v>601045</v>
       </c>
       <c r="R9" t="n">
-        <v>6967962</v>
+        <v>6968150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_426</t>
+          <t>2024_427</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>123321518</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>123321517</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
+        <v>78508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321518</v>
+        <v>123321517</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>78511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,47 +1437,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Larsmyran, Mpd</t>
+          <t>Per-Larsmyren, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601084</v>
+        <v>601045</v>
       </c>
       <c r="R8" t="n">
-        <v>6967962</v>
+        <v>6968150</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_426</t>
+          <t>2024_427</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321517</v>
+        <v>123321518</v>
       </c>
       <c r="B9" t="n">
-        <v>78508</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Larsmyren, Mpd</t>
+          <t>Per-Larsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601045</v>
+        <v>601084</v>
       </c>
       <c r="R9" t="n">
-        <v>6968150</v>
+        <v>6967962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_427</t>
+          <t>2024_426</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>123321517</v>
       </c>
       <c r="B8" t="n">
-        <v>78511</v>
+        <v>78517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>123321518</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>123321517</v>
       </c>
       <c r="B8" t="n">
-        <v>78517</v>
+        <v>78522</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>123321518</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321517</v>
+        <v>123321518</v>
       </c>
       <c r="B8" t="n">
-        <v>78522</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,47 +1437,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Larsmyren, Mpd</t>
+          <t>Per-Larsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601045</v>
+        <v>601084</v>
       </c>
       <c r="R8" t="n">
-        <v>6968150</v>
+        <v>6967962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_427</t>
+          <t>2024_426</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321518</v>
+        <v>123321517</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>78524</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Larsmyran, Mpd</t>
+          <t>Per-Larsmyren, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601084</v>
+        <v>601045</v>
       </c>
       <c r="R9" t="n">
-        <v>6967962</v>
+        <v>6968150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_426</t>
+          <t>2024_427</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>123321518</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321518</v>
+        <v>123321517</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>78524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,47 +1437,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Larsmyran, Mpd</t>
+          <t>Per-Larsmyren, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601084</v>
+        <v>601045</v>
       </c>
       <c r="R8" t="n">
-        <v>6967962</v>
+        <v>6968150</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_426</t>
+          <t>2024_427</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321517</v>
+        <v>123321518</v>
       </c>
       <c r="B9" t="n">
-        <v>78524</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Larsmyren, Mpd</t>
+          <t>Per-Larsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601045</v>
+        <v>601084</v>
       </c>
       <c r="R9" t="n">
-        <v>6968150</v>
+        <v>6967962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_427</t>
+          <t>2024_426</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22228-2023 artfynd.xlsx
+++ b/artfynd/A 22228-2023 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123321517</v>
+        <v>123321518</v>
       </c>
       <c r="B8" t="n">
-        <v>78524</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,47 +1437,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Larsmyren, Mpd</t>
+          <t>Per-Larsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601045</v>
+        <v>601084</v>
       </c>
       <c r="R8" t="n">
-        <v>6968150</v>
+        <v>6967962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_427</t>
+          <t>2024_426</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123321518</v>
+        <v>123321517</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>78524</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Larsmyran, Mpd</t>
+          <t>Per-Larsmyren, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601084</v>
+        <v>601045</v>
       </c>
       <c r="R9" t="n">
-        <v>6967962</v>
+        <v>6968150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_426</t>
+          <t>2024_427</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
